--- a/tests/fixtures/commandes_sap.xlsx
+++ b/tests/fixtures/commandes_sap.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,11 @@
           <t>CCN</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Date d'émission de la commande</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,6 +586,9 @@
       <c r="L5" t="n">
         <v>13</v>
       </c>
+      <c r="M5" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,6 +639,9 @@
       <c r="L6" t="n">
         <v>14</v>
       </c>
+      <c r="M6" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,6 +692,9 @@
       <c r="L7" t="n">
         <v>15</v>
       </c>
+      <c r="M7" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -728,6 +742,9 @@
       <c r="L8" t="n">
         <v>16</v>
       </c>
+      <c r="M8" s="1" t="n">
+        <v>46286</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -778,6 +795,9 @@
       <c r="L9" t="n">
         <v>17</v>
       </c>
+      <c r="M9" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -828,6 +848,9 @@
       <c r="L10" t="n">
         <v>25</v>
       </c>
+      <c r="M10" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -878,6 +901,9 @@
       <c r="L11" t="n">
         <v>20</v>
       </c>
+      <c r="M11" s="1" t="n">
+        <v>46236</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -928,6 +954,9 @@
       <c r="L12" t="n">
         <v>23</v>
       </c>
+      <c r="M12" s="1" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -978,6 +1007,9 @@
       <c r="L13" t="n">
         <v>24</v>
       </c>
+      <c r="M13" s="1" t="n">
+        <v>46297</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1027,6 +1059,57 @@
       </c>
       <c r="L14" t="n">
         <v>24</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FX-1003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CMD-0031</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AC03</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>246</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F003</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>54424</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>En cours</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>13</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>46114</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/commandes_sap.xlsx
+++ b/tests/fixtures/commandes_sap.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,48 +1067,101 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>FM-1004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CMD-0040</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AC20</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>245</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>F031</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fournisseur Tango</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46402</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>En cours</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>150</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>60</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>FX-1003</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>CMD-0031</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>AC03</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>246</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>F003</t>
         </is>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G16" s="1" t="n">
         <v>46174</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>54424</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
         <v>13</v>
       </c>
-      <c r="M15" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>46114</v>
       </c>
     </row>

--- a/tests/fixtures/commandes_sap.xlsx
+++ b/tests/fixtures/commandes_sap.xlsx
@@ -1111,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>7104</v>
       </c>
       <c r="M15" s="1" t="n">
         <v>46297</v>
